--- a/tables/Datas/map.xlsx
+++ b/tables/Datas/map.xlsx
@@ -1358,7 +1358,6 @@
       <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="D6"/>
       <c r="E6">
         <v>1</v>
       </c>
@@ -1366,13 +1365,13 @@
         <v>10001</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>432</v>
       </c>
       <c r="H6">
+        <v>373</v>
+      </c>
+      <c r="I6">
         <v>0</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1382,7 +1381,6 @@
       <c r="C7" t="s">
         <v>22</v>
       </c>
-      <c r="D7"/>
       <c r="E7">
         <v>2</v>
       </c>
@@ -1390,13 +1388,13 @@
         <v>10002</v>
       </c>
       <c r="G7">
-        <v>11</v>
+        <v>432</v>
       </c>
       <c r="H7">
+        <v>373</v>
+      </c>
+      <c r="I7">
         <v>0</v>
-      </c>
-      <c r="I7">
-        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1406,7 +1404,6 @@
       <c r="C8" t="s">
         <v>23</v>
       </c>
-      <c r="D8"/>
       <c r="E8">
         <v>3</v>
       </c>
@@ -1414,13 +1411,13 @@
         <v>10003</v>
       </c>
       <c r="G8">
-        <v>12</v>
+        <v>432</v>
       </c>
       <c r="H8">
+        <v>373</v>
+      </c>
+      <c r="I8">
         <v>0</v>
-      </c>
-      <c r="I8">
-        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1430,7 +1427,6 @@
       <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="D9"/>
       <c r="E9">
         <v>4</v>
       </c>
@@ -1438,13 +1434,13 @@
         <v>10004</v>
       </c>
       <c r="G9">
-        <v>13</v>
+        <v>432</v>
       </c>
       <c r="H9">
+        <v>373</v>
+      </c>
+      <c r="I9">
         <v>0</v>
-      </c>
-      <c r="I9">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1454,7 +1450,6 @@
       <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="D10"/>
       <c r="E10">
         <v>5</v>
       </c>
@@ -1462,13 +1457,13 @@
         <v>10005</v>
       </c>
       <c r="G10">
-        <v>14</v>
+        <v>432</v>
       </c>
       <c r="H10">
+        <v>373</v>
+      </c>
+      <c r="I10">
         <v>0</v>
-      </c>
-      <c r="I10">
-        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1478,7 +1473,6 @@
       <c r="C11" t="s">
         <v>26</v>
       </c>
-      <c r="D11"/>
       <c r="E11">
         <v>6</v>
       </c>
@@ -1486,13 +1480,13 @@
         <v>10006</v>
       </c>
       <c r="G11">
-        <v>15</v>
+        <v>432</v>
       </c>
       <c r="H11">
+        <v>373</v>
+      </c>
+      <c r="I11">
         <v>0</v>
-      </c>
-      <c r="I11">
-        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1502,7 +1496,6 @@
       <c r="C12" t="s">
         <v>27</v>
       </c>
-      <c r="D12"/>
       <c r="E12">
         <v>7</v>
       </c>
@@ -1510,13 +1503,13 @@
         <v>10007</v>
       </c>
       <c r="G12">
-        <v>16</v>
+        <v>432</v>
       </c>
       <c r="H12">
+        <v>373</v>
+      </c>
+      <c r="I12">
         <v>0</v>
-      </c>
-      <c r="I12">
-        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1526,7 +1519,6 @@
       <c r="C13" t="s">
         <v>28</v>
       </c>
-      <c r="D13"/>
       <c r="E13">
         <v>8</v>
       </c>
@@ -1534,13 +1526,13 @@
         <v>10008</v>
       </c>
       <c r="G13">
-        <v>17</v>
+        <v>432</v>
       </c>
       <c r="H13">
+        <v>373</v>
+      </c>
+      <c r="I13">
         <v>0</v>
-      </c>
-      <c r="I13">
-        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1550,7 +1542,6 @@
       <c r="C14" t="s">
         <v>29</v>
       </c>
-      <c r="D14"/>
       <c r="E14">
         <v>9</v>
       </c>
@@ -1558,13 +1549,13 @@
         <v>10009</v>
       </c>
       <c r="G14">
-        <v>18</v>
+        <v>432</v>
       </c>
       <c r="H14">
+        <v>373</v>
+      </c>
+      <c r="I14">
         <v>0</v>
-      </c>
-      <c r="I14">
-        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1574,7 +1565,6 @@
       <c r="C15" t="s">
         <v>30</v>
       </c>
-      <c r="D15"/>
       <c r="E15">
         <v>10</v>
       </c>
@@ -1582,13 +1572,13 @@
         <v>10010</v>
       </c>
       <c r="G15">
-        <v>19</v>
+        <v>432</v>
       </c>
       <c r="H15">
+        <v>373</v>
+      </c>
+      <c r="I15">
         <v>0</v>
-      </c>
-      <c r="I15">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
